--- a/Result/profitability/5345.xlsx
+++ b/Result/profitability/5345.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>-0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1375</v>
+        <v>-0.1287499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-50.34374999999999</v>
+        <v>27.77375000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.32</v>
+        <v>-0.26</v>
       </c>
       <c r="N3" t="n">
-        <v>23.81250000000001</v>
+        <v>18.51625000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-2.63</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5887499999999999</v>
+        <v>-0.5762499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>7.226250000000007</v>
+        <v>8.781250000000009</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7849999999999999</v>
+        <v>-0.7637499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.641249999999993</v>
+        <v>-5.284999999999992</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.925</v>
+        <v>-0.9199999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-16.99624999999999</v>
+        <v>-17.39124999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.54</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1125</v>
+        <v>-1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>-25.32875</v>
+        <v>-25.75374999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.39</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.15875</v>
+        <v>-1.1525</v>
       </c>
       <c r="N8" t="n">
-        <v>-28.70499999999999</v>
+        <v>-30.35499999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-1.15625</v>
       </c>
       <c r="N11" t="n">
-        <v>-28.995</v>
+        <v>-28.99499999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.02</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.825</v>
+        <v>-0.8250000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-16.54999999999999</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5345</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>15</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.11625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-48.6925</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3589883056839815</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.850000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1375482625482627</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
